--- a/data/Confrontos/Semana 4.xlsx
+++ b/data/Confrontos/Semana 4.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luizprado/Downloads/Claude/Campeonato Petz/Confrontos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AAFE411-F40C-2049-A1F6-10406899ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{8AAFE411-F40C-2049-A1F6-10406899ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{706D352E-6D0A-4BD8-B26B-2AF8B0DA51FC}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{995CAAED-AF73-7E48-94DE-E0174A0AC838}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,830 +59,830 @@
     <t>Jogo</t>
   </si>
   <si>
+    <t>BSIA-DF</t>
+  </si>
+  <si>
+    <t>4 x 2</t>
+  </si>
+  <si>
+    <t>MRPG-CE</t>
+  </si>
+  <si>
+    <t>TRSN-PI</t>
+  </si>
+  <si>
+    <t>2 x 4</t>
+  </si>
+  <si>
     <t>RJAF-SP</t>
   </si>
   <si>
+    <t>BQMA-SP</t>
+  </si>
+  <si>
+    <t>CGDE-MS</t>
+  </si>
+  <si>
+    <t>TQTP-AM</t>
+  </si>
+  <si>
+    <t>5 x 1</t>
+  </si>
+  <si>
+    <t>RDLT-SP</t>
+  </si>
+  <si>
+    <t>SLUI-MA</t>
+  </si>
+  <si>
+    <t>6 x 0</t>
+  </si>
+  <si>
+    <t>FBYT-GO</t>
+  </si>
+  <si>
+    <t>ACJU-SE</t>
+  </si>
+  <si>
+    <t>3 x 3</t>
+  </si>
+  <si>
+    <t>EPIA-DF</t>
+  </si>
+  <si>
+    <t>MTLM-PR</t>
+  </si>
+  <si>
+    <t>VISA-RJ</t>
+  </si>
+  <si>
+    <t>JAPE-SP</t>
+  </si>
+  <si>
+    <t>ALPH-SP</t>
+  </si>
+  <si>
+    <t>SMNA-PR</t>
+  </si>
+  <si>
+    <t>ACST-SP</t>
+  </si>
+  <si>
+    <t>CTMN-MG</t>
+  </si>
+  <si>
+    <t>RBFR-RN</t>
+  </si>
+  <si>
+    <t>SMGL-SP</t>
+  </si>
+  <si>
+    <t>POMP-SP</t>
+  </si>
+  <si>
+    <t>JGRE-SP</t>
+  </si>
+  <si>
+    <t>JUZF-MG</t>
+  </si>
+  <si>
+    <t>PQSH-BA</t>
+  </si>
+  <si>
+    <t>SVCT-SP</t>
+  </si>
+  <si>
+    <t>DDMA-SP</t>
+  </si>
+  <si>
+    <t>SERR-ES</t>
+  </si>
+  <si>
+    <t>SOTT-SP</t>
+  </si>
+  <si>
+    <t>TRMS-SP</t>
+  </si>
+  <si>
+    <t>ABNO-RJ</t>
+  </si>
+  <si>
+    <t>MAUA-SP</t>
+  </si>
+  <si>
+    <t>SUBR-MG</t>
+  </si>
+  <si>
+    <t>ITNH-SP</t>
+  </si>
+  <si>
+    <t>TORS-PR</t>
+  </si>
+  <si>
+    <t>ITTU-SP</t>
+  </si>
+  <si>
+    <t>SLPD-RS</t>
+  </si>
+  <si>
+    <t>MCCO-SP</t>
+  </si>
+  <si>
+    <t>SCSU-SP</t>
+  </si>
+  <si>
+    <t>CPIC-SP</t>
+  </si>
+  <si>
+    <t>GAMA-DF</t>
+  </si>
+  <si>
+    <t>ITPT-SP</t>
+  </si>
+  <si>
+    <t>PDTP-SP</t>
+  </si>
+  <si>
+    <t>RPVG-SP</t>
+  </si>
+  <si>
+    <t>VRAO-SP</t>
+  </si>
+  <si>
+    <t>RTMR-SC</t>
+  </si>
+  <si>
+    <t>BTTA-SP</t>
+  </si>
+  <si>
+    <t>JJAU-SP</t>
+  </si>
+  <si>
+    <t>GRUP-SP</t>
+  </si>
+  <si>
+    <t>PSAG-GO</t>
+  </si>
+  <si>
+    <t>VLMA-SP</t>
+  </si>
+  <si>
+    <t>RGRD-RS</t>
+  </si>
+  <si>
+    <t>INTL-SP</t>
+  </si>
+  <si>
+    <t>SMRE-SP</t>
+  </si>
+  <si>
+    <t>PSMC-AL</t>
+  </si>
+  <si>
+    <t>ASPN-SP</t>
+  </si>
+  <si>
+    <t>CGDR-RJ</t>
+  </si>
+  <si>
+    <t>SIND-MG</t>
+  </si>
+  <si>
+    <t>CFTT-SP</t>
+  </si>
+  <si>
+    <t>NDTN-SP</t>
+  </si>
+  <si>
+    <t>PNMR-PE</t>
+  </si>
+  <si>
+    <t>PAMP-MG</t>
+  </si>
+  <si>
+    <t>AUGT-SP</t>
+  </si>
+  <si>
+    <t>BAND-SP</t>
+  </si>
+  <si>
+    <t>NTAL-RN</t>
+  </si>
+  <si>
+    <t>JVLE-SC</t>
+  </si>
+  <si>
+    <t>BAME-RJ</t>
+  </si>
+  <si>
+    <t>SJRP-SP</t>
+  </si>
+  <si>
+    <t>PROT-RS</t>
+  </si>
+  <si>
+    <t>OSAS-SP</t>
+  </si>
+  <si>
+    <t>VLVL-ES</t>
+  </si>
+  <si>
+    <t>FLNP-SC</t>
+  </si>
+  <si>
+    <t>MOOC-SP</t>
+  </si>
+  <si>
+    <t>BAUR-SP</t>
+  </si>
+  <si>
+    <t>UDIA-MG</t>
+  </si>
+  <si>
+    <t>BOVG-PE</t>
+  </si>
+  <si>
+    <t>CRBT-RS</t>
+  </si>
+  <si>
+    <t>CORA-SP</t>
+  </si>
+  <si>
+    <t>WLUI-SP</t>
+  </si>
+  <si>
+    <t>BFGO-RJ</t>
+  </si>
+  <si>
+    <t>OLDA-PE</t>
+  </si>
+  <si>
+    <t>MRNG-PR</t>
+  </si>
+  <si>
+    <t>VMTD-SP</t>
+  </si>
+  <si>
+    <t>JANH-SP</t>
+  </si>
+  <si>
+    <t>VGLV-SP</t>
+  </si>
+  <si>
+    <t>TEOD-SP</t>
+  </si>
+  <si>
+    <t>MNLH-RJ</t>
+  </si>
+  <si>
+    <t>ITTB-SP</t>
+  </si>
+  <si>
+    <t>CLUZ-MG</t>
+  </si>
+  <si>
+    <t>MRMS-SC</t>
+  </si>
+  <si>
+    <t>CGUA-SP</t>
+  </si>
+  <si>
     <t>1 x 5</t>
   </si>
   <si>
-    <t>RBFR-RN</t>
-  </si>
-  <si>
-    <t>TRSN-PI</t>
-  </si>
-  <si>
-    <t>4 x 2</t>
-  </si>
-  <si>
-    <t>BQMA-SP</t>
-  </si>
-  <si>
-    <t>FBYT-GO</t>
-  </si>
-  <si>
-    <t>2 x 4</t>
-  </si>
-  <si>
-    <t>BSIA-DF</t>
-  </si>
-  <si>
-    <t>VISA-RJ</t>
-  </si>
-  <si>
-    <t>SLUI-MA</t>
-  </si>
-  <si>
-    <t>ALPH-SP</t>
-  </si>
-  <si>
-    <t>5 x 1</t>
-  </si>
-  <si>
-    <t>MRPG-CE</t>
-  </si>
-  <si>
-    <t>ACJU-SE</t>
-  </si>
-  <si>
-    <t>TQTP-AM</t>
-  </si>
-  <si>
-    <t>CGDE-MS</t>
-  </si>
-  <si>
-    <t>ACST-SP</t>
-  </si>
-  <si>
-    <t>EPIA-DF</t>
-  </si>
-  <si>
-    <t>3 x 3</t>
-  </si>
-  <si>
-    <t>MTLM-PR</t>
-  </si>
-  <si>
-    <t>SMNA-PR</t>
-  </si>
-  <si>
-    <t>RDLT-SP</t>
-  </si>
-  <si>
-    <t>CTMN-MG</t>
-  </si>
-  <si>
-    <t>JAPE-SP</t>
-  </si>
-  <si>
-    <t>JUZF-MG</t>
-  </si>
-  <si>
-    <t>CPIC-SP</t>
-  </si>
-  <si>
-    <t>JGRE-SP</t>
-  </si>
-  <si>
-    <t>PQSH-BA</t>
-  </si>
-  <si>
-    <t>TRMS-SP</t>
-  </si>
-  <si>
-    <t>SMGL-SP</t>
-  </si>
-  <si>
-    <t>ITNH-SP</t>
-  </si>
-  <si>
-    <t>SOTT-SP</t>
-  </si>
-  <si>
-    <t>ITTU-SP</t>
-  </si>
-  <si>
-    <t>POMP-SP</t>
-  </si>
-  <si>
-    <t>ABNO-RJ</t>
-  </si>
-  <si>
-    <t>DDMA-SP</t>
-  </si>
-  <si>
-    <t>SVCT-SP</t>
-  </si>
-  <si>
-    <t>MCCO-SP</t>
-  </si>
-  <si>
-    <t>MAUA-SP</t>
-  </si>
-  <si>
-    <t>SUBR-MG</t>
-  </si>
-  <si>
-    <t>SLPD-RS</t>
-  </si>
-  <si>
-    <t>SERR-ES</t>
-  </si>
-  <si>
-    <t>SCSU-SP</t>
-  </si>
-  <si>
-    <t>TORS-PR</t>
-  </si>
-  <si>
-    <t>RPVG-SP</t>
-  </si>
-  <si>
-    <t>NDTN-SP</t>
-  </si>
-  <si>
-    <t>PDTP-SP</t>
-  </si>
-  <si>
-    <t>VRAO-SP</t>
-  </si>
-  <si>
-    <t>PSAG-GO</t>
-  </si>
-  <si>
-    <t>GAMA-DF</t>
-  </si>
-  <si>
-    <t>SMRE-SP</t>
-  </si>
-  <si>
-    <t>GRUP-SP</t>
-  </si>
-  <si>
-    <t>ASPN-SP</t>
-  </si>
-  <si>
-    <t>ITPT-SP</t>
-  </si>
-  <si>
-    <t>VLMA-SP</t>
-  </si>
-  <si>
-    <t>BTTA-SP</t>
-  </si>
-  <si>
-    <t>RTMR-SC</t>
-  </si>
-  <si>
-    <t>SIND-MG</t>
-  </si>
-  <si>
-    <t>RGRD-RS</t>
-  </si>
-  <si>
-    <t>INTL-SP</t>
-  </si>
-  <si>
-    <t>CGDR-RJ</t>
-  </si>
-  <si>
-    <t>JJAU-SP</t>
-  </si>
-  <si>
-    <t>CFTT-SP</t>
-  </si>
-  <si>
-    <t>PSMC-AL</t>
-  </si>
-  <si>
-    <t>BAND-SP</t>
-  </si>
-  <si>
-    <t>BFGO-RJ</t>
-  </si>
-  <si>
-    <t>AUGT-SP</t>
-  </si>
-  <si>
-    <t>NTAL-RN</t>
-  </si>
-  <si>
-    <t>OSAS-SP</t>
-  </si>
-  <si>
-    <t>PNMR-PE</t>
-  </si>
-  <si>
-    <t>BAUR-SP</t>
-  </si>
-  <si>
-    <t>PROT-RS</t>
-  </si>
-  <si>
-    <t>BOVG-PE</t>
-  </si>
-  <si>
-    <t>PAMP-MG</t>
-  </si>
-  <si>
-    <t>VLVL-ES</t>
-  </si>
-  <si>
-    <t>BAME-RJ</t>
-  </si>
-  <si>
-    <t>JVLE-SC</t>
-  </si>
-  <si>
-    <t>CORA-SP</t>
-  </si>
-  <si>
-    <t>FLNP-SC</t>
-  </si>
-  <si>
-    <t>MOOC-SP</t>
-  </si>
-  <si>
-    <t>CRBT-RS</t>
-  </si>
-  <si>
-    <t>SJRP-SP</t>
-  </si>
-  <si>
-    <t>WLUI-SP</t>
-  </si>
-  <si>
-    <t>UDIA-MG</t>
-  </si>
-  <si>
-    <t>JANH-SP</t>
+    <t>PIRA-SP</t>
+  </si>
+  <si>
+    <t>IPIR-SP</t>
+  </si>
+  <si>
+    <t>CDJD-SP</t>
+  </si>
+  <si>
+    <t>CATU-PR</t>
+  </si>
+  <si>
+    <t>SPVL-RO</t>
+  </si>
+  <si>
+    <t>JABQ-SP</t>
+  </si>
+  <si>
+    <t>CNTG-MG</t>
+  </si>
+  <si>
+    <t>PGDE-SP</t>
   </si>
   <si>
     <t>ITPC-SP</t>
   </si>
   <si>
-    <t>VMTD-SP</t>
-  </si>
-  <si>
-    <t>VGLV-SP</t>
-  </si>
-  <si>
-    <t>MRMS-SC</t>
-  </si>
-  <si>
-    <t>OLDA-PE</t>
-  </si>
-  <si>
-    <t>CDJD-SP</t>
-  </si>
-  <si>
-    <t>CLUZ-MG</t>
-  </si>
-  <si>
-    <t>SPVL-RO</t>
-  </si>
-  <si>
-    <t>MRNG-PR</t>
-  </si>
-  <si>
-    <t>CGUA-SP</t>
-  </si>
-  <si>
-    <t>MNLH-RJ</t>
-  </si>
-  <si>
-    <t>TEOD-SP</t>
-  </si>
-  <si>
-    <t>CNTG-MG</t>
-  </si>
-  <si>
-    <t>PIRA-SP</t>
-  </si>
-  <si>
-    <t>IPIR-SP</t>
-  </si>
-  <si>
-    <t>JABQ-SP</t>
-  </si>
-  <si>
-    <t>ITTB-SP</t>
-  </si>
-  <si>
-    <t>PGDE-SP</t>
-  </si>
-  <si>
-    <t>CATU-PR</t>
+    <t>PLAV-SP</t>
+  </si>
+  <si>
+    <t>LTIR-PR</t>
+  </si>
+  <si>
+    <t>SJDM-PR</t>
   </si>
   <si>
     <t>TGTG-DF</t>
   </si>
   <si>
+    <t>SPAN-MT</t>
+  </si>
+  <si>
+    <t>HTLD-SP</t>
+  </si>
+  <si>
+    <t>NIGC-RJ</t>
+  </si>
+  <si>
+    <t>ITGU-SC</t>
+  </si>
+  <si>
+    <t>BFRX-RJ</t>
+  </si>
+  <si>
+    <t>LHVD-PR</t>
+  </si>
+  <si>
+    <t>GVLD-MG</t>
+  </si>
+  <si>
+    <t>LTPL-SP</t>
+  </si>
+  <si>
+    <t>CBUI-SP</t>
+  </si>
+  <si>
+    <t>ESTG-GO</t>
+  </si>
+  <si>
+    <t>MTTO-SP</t>
+  </si>
+  <si>
+    <t>GBSL-DF</t>
+  </si>
+  <si>
+    <t>SGSQ-SP</t>
+  </si>
+  <si>
+    <t>BTCT-SP</t>
+  </si>
+  <si>
+    <t>PIND-SP</t>
+  </si>
+  <si>
     <t>NSPL-MS</t>
   </si>
   <si>
-    <t>SJDM-PR</t>
-  </si>
-  <si>
-    <t>SPAN-MT</t>
-  </si>
-  <si>
-    <t>LHVD-PR</t>
-  </si>
-  <si>
-    <t>PLAV-SP</t>
-  </si>
-  <si>
-    <t>ESTG-GO</t>
-  </si>
-  <si>
-    <t>BFRX-RJ</t>
-  </si>
-  <si>
-    <t>GBSL-DF</t>
-  </si>
-  <si>
-    <t>LTIR-PR</t>
-  </si>
-  <si>
-    <t>GVLD-MG</t>
-  </si>
-  <si>
-    <t>NIGC-RJ</t>
-  </si>
-  <si>
-    <t>HTLD-SP</t>
-  </si>
-  <si>
-    <t>BTCT-SP</t>
-  </si>
-  <si>
-    <t>LTPL-SP</t>
-  </si>
-  <si>
-    <t>CBUI-SP</t>
-  </si>
-  <si>
-    <t>SGSQ-SP</t>
-  </si>
-  <si>
-    <t>ITGU-SC</t>
-  </si>
-  <si>
-    <t>PIND-SP</t>
-  </si>
-  <si>
-    <t>MTTO-SP</t>
+    <t>MOGI-SP</t>
+  </si>
+  <si>
+    <t>ANHM-SP</t>
+  </si>
+  <si>
+    <t>VTRA-ES</t>
   </si>
   <si>
     <t>PRLA-BA</t>
   </si>
   <si>
+    <t>ITAM-SP</t>
+  </si>
+  <si>
+    <t>MGST-MT</t>
+  </si>
+  <si>
+    <t>BALN-SC</t>
+  </si>
+  <si>
+    <t>EDFC-SP</t>
+  </si>
+  <si>
+    <t>TMBO-SP</t>
+  </si>
+  <si>
+    <t>BLUM-SC</t>
+  </si>
+  <si>
+    <t>MCNA-RJ</t>
+  </si>
+  <si>
+    <t>JDIC-RJ</t>
+  </si>
+  <si>
+    <t>KNDY-CE</t>
+  </si>
+  <si>
+    <t>MRBI-SP</t>
+  </si>
+  <si>
+    <t>TBAO-SP</t>
+  </si>
+  <si>
+    <t>PVRD-AL</t>
+  </si>
+  <si>
+    <t>GPIR-SP</t>
+  </si>
+  <si>
+    <t>AGMN-PE</t>
+  </si>
+  <si>
+    <t>LMAO-SP</t>
+  </si>
+  <si>
     <t>FOZI-PR</t>
   </si>
   <si>
-    <t>VTRA-ES</t>
-  </si>
-  <si>
-    <t>ITAM-SP</t>
-  </si>
-  <si>
-    <t>BLUM-SC</t>
-  </si>
-  <si>
-    <t>MOGI-SP</t>
-  </si>
-  <si>
-    <t>MRBI-SP</t>
-  </si>
-  <si>
-    <t>TMBO-SP</t>
-  </si>
-  <si>
-    <t>PVRD-AL</t>
-  </si>
-  <si>
-    <t>ANHM-SP</t>
-  </si>
-  <si>
-    <t>MCNA-RJ</t>
-  </si>
-  <si>
-    <t>BALN-SC</t>
-  </si>
-  <si>
-    <t>MGST-MT</t>
-  </si>
-  <si>
-    <t>AGMN-PE</t>
-  </si>
-  <si>
-    <t>JDIC-RJ</t>
-  </si>
-  <si>
-    <t>KNDY-CE</t>
-  </si>
-  <si>
-    <t>GPIR-SP</t>
-  </si>
-  <si>
-    <t>EDFC-SP</t>
-  </si>
-  <si>
-    <t>LMAO-SP</t>
-  </si>
-  <si>
-    <t>TBAO-SP</t>
+    <t>ACTN-MG</t>
+  </si>
+  <si>
+    <t>BTIM-MG</t>
+  </si>
+  <si>
+    <t>ACLM-SP</t>
   </si>
   <si>
     <t>NHBG-RS</t>
   </si>
   <si>
+    <t>PCBU-SP</t>
+  </si>
+  <si>
+    <t>MGYA-SP</t>
+  </si>
+  <si>
+    <t>JPES-PB</t>
+  </si>
+  <si>
+    <t>CTTE-SC</t>
+  </si>
+  <si>
+    <t>DNTC-RS</t>
+  </si>
+  <si>
+    <t>CCVE-PR</t>
+  </si>
+  <si>
+    <t>STAD-SP</t>
+  </si>
+  <si>
+    <t>GRLH-SP</t>
+  </si>
+  <si>
+    <t>CDIA-DF</t>
+  </si>
+  <si>
+    <t>RBAV-RS</t>
+  </si>
+  <si>
+    <t>ITJI-SC</t>
+  </si>
+  <si>
+    <t>JUND-SP</t>
+  </si>
+  <si>
+    <t>CVDA-RS</t>
+  </si>
+  <si>
+    <t>LAUZ-SP</t>
+  </si>
+  <si>
+    <t>JDBT-RJ</t>
+  </si>
+  <si>
     <t>GVGC-SP</t>
   </si>
   <si>
-    <t>ACLM-SP</t>
-  </si>
-  <si>
-    <t>PCBU-SP</t>
-  </si>
-  <si>
-    <t>CCVE-PR</t>
+    <t>RICL-SP</t>
+  </si>
+  <si>
+    <t>SADP-SP</t>
+  </si>
+  <si>
+    <t>NCUN-SP</t>
+  </si>
+  <si>
+    <t>STLG-MG</t>
+  </si>
+  <si>
+    <t>JABT-PE</t>
+  </si>
+  <si>
+    <t>CCMA-SC</t>
+  </si>
+  <si>
+    <t>SCAR-SP</t>
   </si>
   <si>
     <t>0 x 6</t>
   </si>
   <si>
-    <t>ACTN-MG</t>
-  </si>
-  <si>
-    <t>RBAV-RS</t>
-  </si>
-  <si>
-    <t>DNTC-RS</t>
-  </si>
-  <si>
-    <t>JUND-SP</t>
-  </si>
-  <si>
-    <t>BTIM-MG</t>
-  </si>
-  <si>
-    <t>STAD-SP</t>
-  </si>
-  <si>
-    <t>JPES-PB</t>
-  </si>
-  <si>
-    <t>MGYA-SP</t>
-  </si>
-  <si>
-    <t>LAUZ-SP</t>
-  </si>
-  <si>
-    <t>GRLH-SP</t>
-  </si>
-  <si>
-    <t>CDIA-DF</t>
-  </si>
-  <si>
-    <t>CVDA-RS</t>
-  </si>
-  <si>
-    <t>CTTE-SC</t>
-  </si>
-  <si>
-    <t>JDBT-RJ</t>
-  </si>
-  <si>
-    <t>ITJI-SC</t>
-  </si>
-  <si>
-    <t>STLG-MG</t>
+    <t>ARAC-SP</t>
+  </si>
+  <si>
+    <t>SHGR-RJ</t>
+  </si>
+  <si>
+    <t>CPCB-RJ</t>
+  </si>
+  <si>
+    <t>CTJC-MG</t>
+  </si>
+  <si>
+    <t>SJCK-PR</t>
+  </si>
+  <si>
+    <t>BGCV-RS</t>
+  </si>
+  <si>
+    <t>UBRB-MG</t>
+  </si>
+  <si>
+    <t>GRVT-RS</t>
+  </si>
+  <si>
+    <t>IGES-SP</t>
+  </si>
+  <si>
+    <t>RPTO-SP</t>
+  </si>
+  <si>
+    <t>IPTG-MG</t>
+  </si>
+  <si>
+    <t>JCRI-SP</t>
   </si>
   <si>
     <t>HPSL-SE</t>
   </si>
   <si>
-    <t>NCUN-SP</t>
-  </si>
-  <si>
-    <t>JABT-PE</t>
-  </si>
-  <si>
-    <t>CPCB-RJ</t>
-  </si>
-  <si>
-    <t>RICL-SP</t>
-  </si>
-  <si>
-    <t>UBRB-MG</t>
-  </si>
-  <si>
-    <t>SHGR-RJ</t>
-  </si>
-  <si>
-    <t>IGES-SP</t>
-  </si>
-  <si>
-    <t>SADP-SP</t>
-  </si>
-  <si>
-    <t>CTJC-MG</t>
-  </si>
-  <si>
-    <t>SCAR-SP</t>
-  </si>
-  <si>
-    <t>CCMA-SC</t>
-  </si>
-  <si>
-    <t>IPTG-MG</t>
-  </si>
-  <si>
-    <t>SJCK-PR</t>
-  </si>
-  <si>
-    <t>BGCV-RS</t>
-  </si>
-  <si>
-    <t>RPTO-SP</t>
-  </si>
-  <si>
-    <t>ARAC-SP</t>
-  </si>
-  <si>
-    <t>JCRI-SP</t>
-  </si>
-  <si>
-    <t>GRVT-RS</t>
+    <t>ASTS-SP</t>
+  </si>
+  <si>
+    <t>BNOC-BA</t>
+  </si>
+  <si>
+    <t>NSCA-MG</t>
   </si>
   <si>
     <t>DJBA-AM</t>
   </si>
   <si>
+    <t>BT63-GO</t>
+  </si>
+  <si>
+    <t>FCOR-MT</t>
+  </si>
+  <si>
+    <t>W3NT-DF</t>
+  </si>
+  <si>
+    <t>ABVT-SP</t>
+  </si>
+  <si>
+    <t>CGHS-SP</t>
+  </si>
+  <si>
+    <t>ALDT-CE</t>
+  </si>
+  <si>
+    <t>AFCO-SP</t>
+  </si>
+  <si>
+    <t>SCBA-SP</t>
+  </si>
+  <si>
+    <t>STCE-SP</t>
+  </si>
+  <si>
+    <t>RAJA-MG</t>
+  </si>
+  <si>
+    <t>MOIN-RS</t>
+  </si>
+  <si>
+    <t>ASAN-DF</t>
+  </si>
+  <si>
+    <t>PMAS-TO</t>
+  </si>
+  <si>
+    <t>BLEM-PA</t>
+  </si>
+  <si>
+    <t>CTIA-SP</t>
+  </si>
+  <si>
     <t>TIET-SP</t>
   </si>
   <si>
-    <t>NSCA-MG</t>
-  </si>
-  <si>
-    <t>BT63-GO</t>
-  </si>
-  <si>
-    <t>ALDT-CE</t>
-  </si>
-  <si>
-    <t>ASTS-SP</t>
-  </si>
-  <si>
-    <t>RAJA-MG</t>
-  </si>
-  <si>
-    <t>CGHS-SP</t>
-  </si>
-  <si>
-    <t>ASAN-DF</t>
-  </si>
-  <si>
-    <t>6 x 0</t>
-  </si>
-  <si>
-    <t>BNOC-BA</t>
-  </si>
-  <si>
-    <t>AFCO-SP</t>
-  </si>
-  <si>
-    <t>W3NT-DF</t>
-  </si>
-  <si>
-    <t>FCOR-MT</t>
-  </si>
-  <si>
-    <t>BLEM-PA</t>
-  </si>
-  <si>
-    <t>SCBA-SP</t>
-  </si>
-  <si>
-    <t>STCE-SP</t>
-  </si>
-  <si>
-    <t>PMAS-TO</t>
-  </si>
-  <si>
-    <t>ABVT-SP</t>
-  </si>
-  <si>
-    <t>CTIA-SP</t>
-  </si>
-  <si>
-    <t>MOIN-RS</t>
+    <t>GUJA-SP</t>
+  </si>
+  <si>
+    <t>CNOA-RS</t>
+  </si>
+  <si>
+    <t>PTBA-BA</t>
   </si>
   <si>
     <t>ACLR-DF</t>
   </si>
   <si>
+    <t>BJDB-DF</t>
+  </si>
+  <si>
+    <t>JFIR-SP</t>
+  </si>
+  <si>
+    <t>STDU-CE</t>
+  </si>
+  <si>
+    <t>CPCO-SC</t>
+  </si>
+  <si>
+    <t>CXAS-RS</t>
+  </si>
+  <si>
+    <t>FRCA-SP</t>
+  </si>
+  <si>
+    <t>PBAR-SP</t>
+  </si>
+  <si>
+    <t>AFPN-MS</t>
+  </si>
+  <si>
+    <t>TTVL-SP</t>
+  </si>
+  <si>
+    <t>PCCD-MG</t>
+  </si>
+  <si>
+    <t>STMA-RS</t>
+  </si>
+  <si>
+    <t>AMRC-RJ</t>
+  </si>
+  <si>
+    <t>WSOA-CE</t>
+  </si>
+  <si>
+    <t>VCQT-BA</t>
+  </si>
+  <si>
+    <t>CTLO-MG</t>
+  </si>
+  <si>
     <t>PLOT-RS</t>
   </si>
   <si>
-    <t>PTBA-BA</t>
-  </si>
-  <si>
-    <t>BJDB-DF</t>
-  </si>
-  <si>
-    <t>FRCA-SP</t>
-  </si>
-  <si>
-    <t>GUJA-SP</t>
-  </si>
-  <si>
-    <t>PCCD-MG</t>
-  </si>
-  <si>
-    <t>CXAS-RS</t>
-  </si>
-  <si>
-    <t>AMRC-RJ</t>
-  </si>
-  <si>
-    <t>CNOA-RS</t>
-  </si>
-  <si>
-    <t>PBAR-SP</t>
-  </si>
-  <si>
-    <t>STDU-CE</t>
-  </si>
-  <si>
-    <t>JFIR-SP</t>
-  </si>
-  <si>
-    <t>VCQT-BA</t>
-  </si>
-  <si>
-    <t>AFPN-MS</t>
-  </si>
-  <si>
-    <t>TTVL-SP</t>
-  </si>
-  <si>
-    <t>WSOA-CE</t>
-  </si>
-  <si>
-    <t>CPCO-SC</t>
-  </si>
-  <si>
-    <t>CTLO-MG</t>
-  </si>
-  <si>
-    <t>STMA-RS</t>
+    <t>BRSQ-SC</t>
+  </si>
+  <si>
+    <t>ANCH-SP</t>
+  </si>
+  <si>
+    <t>ANGL-SP</t>
   </si>
   <si>
     <t>ENSD-SP</t>
   </si>
   <si>
+    <t>SMOC-SP</t>
+  </si>
+  <si>
+    <t>ILHG-RJ</t>
+  </si>
+  <si>
+    <t>PRUD-SP</t>
+  </si>
+  <si>
+    <t>NTZN-RN</t>
+  </si>
+  <si>
+    <t>SBCA-SP</t>
+  </si>
+  <si>
+    <t>SVBD-MG</t>
+  </si>
+  <si>
+    <t>ACTB-GO</t>
+  </si>
+  <si>
+    <t>TTCP-SP</t>
+  </si>
+  <si>
+    <t>BARR-MG</t>
+  </si>
+  <si>
+    <t>GVDL-SP</t>
+  </si>
+  <si>
+    <t>AVGO-SP</t>
+  </si>
+  <si>
+    <t>RMAR-PE</t>
+  </si>
+  <si>
+    <t>FVCL-SP</t>
+  </si>
+  <si>
+    <t>RPIN-SP</t>
+  </si>
+  <si>
+    <t>CPNS-SP</t>
+  </si>
+  <si>
     <t>VGDE-MT</t>
   </si>
   <si>
-    <t>ANGL-SP</t>
-  </si>
-  <si>
-    <t>SMOC-SP</t>
-  </si>
-  <si>
-    <t>SVBD-MG</t>
-  </si>
-  <si>
-    <t>BRSQ-SC</t>
-  </si>
-  <si>
-    <t>GVDL-SP</t>
-  </si>
-  <si>
-    <t>SBCA-SP</t>
-  </si>
-  <si>
-    <t>RMAR-PE</t>
-  </si>
-  <si>
-    <t>ANCH-SP</t>
-  </si>
-  <si>
-    <t>ACTB-GO</t>
-  </si>
-  <si>
-    <t>PRUD-SP</t>
-  </si>
-  <si>
-    <t>ILHG-RJ</t>
-  </si>
-  <si>
-    <t>RPIN-SP</t>
-  </si>
-  <si>
-    <t>TTCP-SP</t>
-  </si>
-  <si>
-    <t>BARR-MG</t>
-  </si>
-  <si>
-    <t>FVCL-SP</t>
-  </si>
-  <si>
-    <t>NTZN-RN</t>
-  </si>
-  <si>
-    <t>CPNS-SP</t>
-  </si>
-  <si>
-    <t>AVGO-SP</t>
-  </si>
-  <si>
     <t>DVNP-MG</t>
   </si>
   <si>
+    <t>VALP-GO</t>
+  </si>
+  <si>
     <t>AMER-SP</t>
   </si>
   <si>
+    <t>ARUJ-SP</t>
+  </si>
+  <si>
     <t>SMBA-DF</t>
   </si>
   <si>
-    <t>VALP-GO</t>
+    <t>CMCD-MG</t>
   </si>
   <si>
     <t>ASAC-SP</t>
   </si>
   <si>
-    <t>ARUJ-SP</t>
+    <t>RVDE-GO</t>
   </si>
   <si>
     <t>BNGU-RJ</t>
   </si>
   <si>
-    <t>CMCD-MG</t>
+    <t>DOMP-SP</t>
   </si>
   <si>
     <t>AVML-GO</t>
   </si>
   <si>
-    <t>RVDE-GO</t>
+    <t>INDT-SP</t>
   </si>
   <si>
     <t>SGPZ-SP</t>
   </si>
   <si>
-    <t>DOMP-SP</t>
-  </si>
-  <si>
     <t>AEST-SP</t>
   </si>
   <si>
-    <t>INDT-SP</t>
-  </si>
-  <si>
     <t>PKSB-DF</t>
   </si>
   <si>
+    <t>TTUI-SP</t>
+  </si>
+  <si>
     <t>SCVL-SP</t>
   </si>
   <si>
+    <t>ARRQ-SP</t>
+  </si>
+  <si>
     <t>DRDS-MS</t>
   </si>
   <si>
-    <t>TTUI-SP</t>
+    <t>CLNS-SP</t>
   </si>
   <si>
     <t>ZVJD-SP</t>
   </si>
   <si>
-    <t>ARRQ-SP</t>
+    <t>MGGU-SP</t>
   </si>
   <si>
     <t>ZBND-MG</t>
   </si>
   <si>
-    <t>CLNS-SP</t>
+    <t>COSA-SP</t>
   </si>
   <si>
     <t>SZNO-SP</t>
   </si>
   <si>
-    <t>MGGU-SP</t>
-  </si>
-  <si>
     <t>SBAR-SP</t>
-  </si>
-  <si>
-    <t>COSA-SP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1248,9 +1248,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079210DA-51FE-9C42-8760-D65A34782DC0}">
   <dimension ref="A1:E135"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1267,17 +1267,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>400</v>
+        <v>533</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1289,12 +1289,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>401</v>
+        <v>534</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -1306,46 +1306,46 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>402</v>
+        <v>535</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>536</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>403</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>404</v>
+        <v>537</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -1357,199 +1357,199 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>405</v>
+        <v>538</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>539</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>406</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
       <c r="E9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
       <c r="B10">
-        <v>407</v>
+        <v>540</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11">
-        <v>408</v>
+        <v>541</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12">
-        <v>409</v>
+        <v>542</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
       <c r="B13">
-        <v>410</v>
+        <v>543</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14">
-        <v>411</v>
+        <v>544</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>5</v>
       </c>
       <c r="B15">
-        <v>412</v>
+        <v>545</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16">
-        <v>413</v>
+        <v>546</v>
       </c>
       <c r="C16" t="s">
         <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>5</v>
       </c>
       <c r="B17">
-        <v>414</v>
+        <v>547</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>5</v>
       </c>
       <c r="B18">
-        <v>415</v>
+        <v>548</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>5</v>
       </c>
       <c r="B19">
-        <v>416</v>
+        <v>549</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
@@ -1561,301 +1561,301 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>5</v>
       </c>
       <c r="B20">
-        <v>417</v>
+        <v>550</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>5</v>
       </c>
       <c r="B21">
-        <v>418</v>
+        <v>551</v>
       </c>
       <c r="C21" t="s">
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>5</v>
       </c>
       <c r="B22">
-        <v>419</v>
+        <v>552</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23">
-        <v>420</v>
+        <v>553</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>5</v>
       </c>
       <c r="B24">
-        <v>421</v>
+        <v>554</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>5</v>
       </c>
       <c r="B25">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>5</v>
       </c>
       <c r="B26">
-        <v>423</v>
+        <v>556</v>
       </c>
       <c r="C26" t="s">
         <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>5</v>
       </c>
       <c r="B27">
-        <v>424</v>
+        <v>557</v>
       </c>
       <c r="C27" t="s">
         <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28">
-        <v>425</v>
+        <v>558</v>
       </c>
       <c r="C28" t="s">
         <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>5</v>
       </c>
       <c r="B29">
-        <v>426</v>
+        <v>559</v>
       </c>
       <c r="C29" t="s">
         <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>5</v>
       </c>
       <c r="B30">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="C30" t="s">
         <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="C31" t="s">
         <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="C32" t="s">
         <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>5</v>
       </c>
       <c r="B33">
-        <v>430</v>
+        <v>563</v>
       </c>
       <c r="C33" t="s">
         <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>5</v>
       </c>
       <c r="B34">
-        <v>431</v>
+        <v>564</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>5</v>
       </c>
       <c r="B35">
-        <v>432</v>
+        <v>565</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
       <c r="B36">
-        <v>433</v>
+        <v>566</v>
       </c>
       <c r="C36" t="s">
         <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>5</v>
       </c>
       <c r="B37">
-        <v>434</v>
+        <v>567</v>
       </c>
       <c r="C37" t="s">
         <v>79</v>
@@ -1867,658 +1867,658 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
       <c r="B38">
-        <v>435</v>
+        <v>568</v>
       </c>
       <c r="C38" t="s">
         <v>81</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39">
-        <v>436</v>
+        <v>569</v>
       </c>
       <c r="C39" t="s">
         <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>5</v>
       </c>
       <c r="B40">
-        <v>437</v>
+        <v>570</v>
       </c>
       <c r="C40" t="s">
         <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>5</v>
       </c>
       <c r="B41">
-        <v>438</v>
+        <v>571</v>
       </c>
       <c r="C41" t="s">
         <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>5</v>
       </c>
       <c r="B42">
-        <v>439</v>
+        <v>572</v>
       </c>
       <c r="C42" t="s">
         <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>5</v>
       </c>
       <c r="B43">
-        <v>440</v>
+        <v>573</v>
       </c>
       <c r="C43" t="s">
         <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>5</v>
       </c>
       <c r="B44">
-        <v>441</v>
+        <v>574</v>
       </c>
       <c r="C44" t="s">
         <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>5</v>
       </c>
       <c r="B45">
-        <v>442</v>
+        <v>575</v>
       </c>
       <c r="C45" t="s">
         <v>95</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E45" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>5</v>
       </c>
       <c r="B46">
-        <v>443</v>
+        <v>576</v>
       </c>
       <c r="C46" t="s">
         <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>5</v>
       </c>
       <c r="B47">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="C47" t="s">
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E47" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>5</v>
       </c>
       <c r="B48">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="C48" t="s">
         <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49">
+        <v>579</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50">
+        <v>580</v>
+      </c>
+      <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51">
+        <v>581</v>
+      </c>
+      <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52">
+        <v>582</v>
+      </c>
+      <c r="C52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>583</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54">
+        <v>584</v>
+      </c>
+      <c r="C54" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49">
-        <v>446</v>
-      </c>
-      <c r="C49" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50">
-        <v>447</v>
-      </c>
-      <c r="C50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51">
-        <v>448</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>5</v>
-      </c>
-      <c r="B52">
-        <v>449</v>
-      </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53">
-        <v>450</v>
-      </c>
-      <c r="C53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>5</v>
-      </c>
-      <c r="B54">
-        <v>451</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>25</v>
-      </c>
       <c r="E54" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>5</v>
       </c>
       <c r="B55">
-        <v>452</v>
+        <v>585</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>5</v>
       </c>
       <c r="B56">
-        <v>453</v>
+        <v>586</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>5</v>
       </c>
       <c r="B57">
-        <v>454</v>
+        <v>587</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>5</v>
       </c>
       <c r="B58">
-        <v>455</v>
+        <v>588</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59">
+        <v>589</v>
+      </c>
+      <c r="C59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60">
+        <v>590</v>
+      </c>
+      <c r="C60" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" t="s">
+        <v>102</v>
+      </c>
+      <c r="E60" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61">
+        <v>591</v>
+      </c>
+      <c r="C61" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E61" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>592</v>
+      </c>
+      <c r="C62" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" t="s">
         <v>10</v>
       </c>
-      <c r="E58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59">
-        <v>456</v>
-      </c>
-      <c r="C59" t="s">
-        <v>123</v>
-      </c>
-      <c r="D59" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60">
-        <v>457</v>
-      </c>
-      <c r="C60" t="s">
-        <v>125</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E62" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>593</v>
+      </c>
+      <c r="C63" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" t="s">
         <v>10</v>
       </c>
-      <c r="E60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61">
-        <v>458</v>
-      </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>5</v>
-      </c>
-      <c r="B62">
-        <v>459</v>
-      </c>
-      <c r="C62" t="s">
-        <v>129</v>
-      </c>
-      <c r="D62" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>5</v>
-      </c>
-      <c r="B63">
-        <v>460</v>
-      </c>
-      <c r="C63" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" t="s">
-        <v>25</v>
-      </c>
       <c r="E63" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>5</v>
       </c>
       <c r="B64">
-        <v>461</v>
+        <v>594</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>5</v>
       </c>
       <c r="B65">
-        <v>462</v>
+        <v>595</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>5</v>
       </c>
       <c r="B66">
-        <v>463</v>
+        <v>596</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>5</v>
       </c>
       <c r="B67">
-        <v>464</v>
+        <v>597</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D67" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>598</v>
+      </c>
+      <c r="C68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" t="s">
         <v>10</v>
       </c>
-      <c r="E67" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68">
-        <v>465</v>
-      </c>
-      <c r="C68" t="s">
-        <v>141</v>
-      </c>
-      <c r="D68" t="s">
-        <v>13</v>
-      </c>
       <c r="E68" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>5</v>
       </c>
       <c r="B69">
-        <v>466</v>
+        <v>599</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E69" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>5</v>
       </c>
       <c r="B70">
-        <v>467</v>
+        <v>600</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>601</v>
+      </c>
+      <c r="C71" t="s">
+        <v>148</v>
+      </c>
+      <c r="D71" t="s">
         <v>10</v>
       </c>
-      <c r="E70" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71">
-        <v>468</v>
-      </c>
-      <c r="C71" t="s">
-        <v>147</v>
-      </c>
-      <c r="D71" t="s">
-        <v>25</v>
-      </c>
       <c r="E71" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>5</v>
       </c>
       <c r="B72">
-        <v>469</v>
+        <v>602</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>5</v>
       </c>
       <c r="B73">
-        <v>470</v>
+        <v>603</v>
       </c>
       <c r="C73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>5</v>
       </c>
       <c r="B74">
-        <v>471</v>
+        <v>604</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>5</v>
       </c>
       <c r="B75">
-        <v>472</v>
+        <v>605</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E75" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>5</v>
       </c>
       <c r="B76">
-        <v>473</v>
+        <v>606</v>
       </c>
       <c r="C76" t="s">
         <v>158</v>
@@ -2530,148 +2530,148 @@
         <v>159</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>5</v>
       </c>
       <c r="B77">
-        <v>474</v>
+        <v>607</v>
       </c>
       <c r="C77" t="s">
         <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
       <c r="B78">
-        <v>475</v>
+        <v>608</v>
       </c>
       <c r="C78" t="s">
         <v>162</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>5</v>
       </c>
       <c r="B79">
-        <v>476</v>
+        <v>609</v>
       </c>
       <c r="C79" t="s">
         <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="E79" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>5</v>
       </c>
       <c r="B80">
-        <v>477</v>
+        <v>610</v>
       </c>
       <c r="C80" t="s">
         <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E80" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>5</v>
       </c>
       <c r="B81">
-        <v>478</v>
+        <v>611</v>
       </c>
       <c r="C81" t="s">
         <v>168</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E81" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>5</v>
       </c>
       <c r="B82">
-        <v>479</v>
+        <v>612</v>
       </c>
       <c r="C82" t="s">
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>5</v>
       </c>
       <c r="B83">
-        <v>480</v>
+        <v>613</v>
       </c>
       <c r="C83" t="s">
         <v>172</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>5</v>
       </c>
       <c r="B84">
-        <v>481</v>
+        <v>614</v>
       </c>
       <c r="C84" t="s">
         <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>5</v>
       </c>
       <c r="B85">
-        <v>482</v>
+        <v>615</v>
       </c>
       <c r="C85" t="s">
         <v>176</v>
@@ -2683,216 +2683,216 @@
         <v>177</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>5</v>
       </c>
       <c r="B86">
-        <v>483</v>
+        <v>616</v>
       </c>
       <c r="C86" t="s">
         <v>178</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="E86" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>5</v>
       </c>
       <c r="B87">
-        <v>484</v>
+        <v>617</v>
       </c>
       <c r="C87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>5</v>
       </c>
       <c r="B88">
-        <v>485</v>
+        <v>618</v>
       </c>
       <c r="C88" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D88" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89">
+        <v>619</v>
+      </c>
+      <c r="C89" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" t="s">
         <v>10</v>
       </c>
-      <c r="E88" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>5</v>
-      </c>
-      <c r="B89">
-        <v>486</v>
-      </c>
-      <c r="C89" t="s">
-        <v>184</v>
-      </c>
-      <c r="D89" t="s">
-        <v>13</v>
-      </c>
       <c r="E89" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>5</v>
       </c>
       <c r="B90">
-        <v>487</v>
+        <v>620</v>
       </c>
       <c r="C90" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91">
+        <v>621</v>
+      </c>
+      <c r="C91" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92">
+        <v>622</v>
+      </c>
+      <c r="C92" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" t="s">
+        <v>21</v>
+      </c>
+      <c r="E92" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93">
+        <v>623</v>
+      </c>
+      <c r="C93" t="s">
+        <v>193</v>
+      </c>
+      <c r="D93" t="s">
         <v>10</v>
       </c>
-      <c r="E90" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91">
-        <v>488</v>
-      </c>
-      <c r="C91" t="s">
-        <v>188</v>
-      </c>
-      <c r="D91" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>5</v>
-      </c>
-      <c r="B92">
-        <v>489</v>
-      </c>
-      <c r="C92" t="s">
-        <v>190</v>
-      </c>
-      <c r="D92" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>5</v>
-      </c>
-      <c r="B93">
-        <v>490</v>
-      </c>
-      <c r="C93" t="s">
-        <v>192</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
-      </c>
       <c r="E93" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>5</v>
       </c>
       <c r="B94">
-        <v>491</v>
+        <v>624</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>5</v>
       </c>
       <c r="B95">
-        <v>492</v>
+        <v>625</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>5</v>
       </c>
       <c r="B96">
-        <v>493</v>
+        <v>626</v>
       </c>
       <c r="C96" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>5</v>
       </c>
       <c r="B97">
-        <v>494</v>
+        <v>627</v>
       </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E97" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>5</v>
       </c>
       <c r="B98">
-        <v>495</v>
+        <v>628</v>
       </c>
       <c r="C98" t="s">
         <v>203</v>
@@ -2904,114 +2904,114 @@
         <v>204</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>5</v>
       </c>
       <c r="B99">
-        <v>496</v>
+        <v>629</v>
       </c>
       <c r="C99" t="s">
         <v>205</v>
       </c>
       <c r="D99" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>5</v>
       </c>
       <c r="B100">
-        <v>497</v>
+        <v>630</v>
       </c>
       <c r="C100" t="s">
         <v>207</v>
       </c>
       <c r="D100" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>5</v>
       </c>
       <c r="B101">
-        <v>498</v>
+        <v>631</v>
       </c>
       <c r="C101" t="s">
         <v>209</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>5</v>
       </c>
       <c r="B102">
-        <v>499</v>
+        <v>632</v>
       </c>
       <c r="C102" t="s">
         <v>211</v>
       </c>
       <c r="D102" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>5</v>
       </c>
       <c r="B103">
-        <v>500</v>
+        <v>633</v>
       </c>
       <c r="C103" t="s">
         <v>213</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>5</v>
       </c>
       <c r="B104">
-        <v>501</v>
+        <v>634</v>
       </c>
       <c r="C104" t="s">
         <v>215</v>
       </c>
       <c r="D104" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E104" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>5</v>
       </c>
       <c r="B105">
-        <v>502</v>
+        <v>635</v>
       </c>
       <c r="C105" t="s">
         <v>217</v>
@@ -3023,233 +3023,233 @@
         <v>218</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>5</v>
       </c>
       <c r="B106">
-        <v>503</v>
+        <v>636</v>
       </c>
       <c r="C106" t="s">
         <v>219</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>5</v>
       </c>
       <c r="B107">
-        <v>504</v>
+        <v>637</v>
       </c>
       <c r="C107" t="s">
         <v>221</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E107" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>5</v>
       </c>
       <c r="B108">
-        <v>505</v>
+        <v>638</v>
       </c>
       <c r="C108" t="s">
         <v>223</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>5</v>
       </c>
       <c r="B109">
-        <v>506</v>
+        <v>639</v>
       </c>
       <c r="C109" t="s">
         <v>225</v>
       </c>
       <c r="D109" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E109" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>5</v>
       </c>
       <c r="B110">
-        <v>507</v>
+        <v>640</v>
       </c>
       <c r="C110" t="s">
         <v>227</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>5</v>
       </c>
       <c r="B111">
-        <v>508</v>
+        <v>641</v>
       </c>
       <c r="C111" t="s">
         <v>229</v>
       </c>
       <c r="D111" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E111" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>5</v>
       </c>
       <c r="B112">
-        <v>509</v>
+        <v>642</v>
       </c>
       <c r="C112" t="s">
         <v>231</v>
       </c>
       <c r="D112" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="E112" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>5</v>
       </c>
       <c r="B113">
-        <v>510</v>
+        <v>643</v>
       </c>
       <c r="C113" t="s">
         <v>233</v>
       </c>
       <c r="D113" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E113" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>5</v>
       </c>
       <c r="B114">
-        <v>511</v>
+        <v>644</v>
       </c>
       <c r="C114" t="s">
         <v>235</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>5</v>
       </c>
       <c r="B115">
-        <v>512</v>
+        <v>645</v>
       </c>
       <c r="C115" t="s">
         <v>237</v>
       </c>
       <c r="D115" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>5</v>
       </c>
       <c r="B116">
-        <v>513</v>
+        <v>646</v>
       </c>
       <c r="C116" t="s">
         <v>239</v>
       </c>
       <c r="D116" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E116" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>5</v>
       </c>
       <c r="B117">
-        <v>514</v>
+        <v>647</v>
       </c>
       <c r="C117" t="s">
         <v>241</v>
       </c>
       <c r="D117" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E117" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>5</v>
       </c>
       <c r="B118">
-        <v>515</v>
+        <v>648</v>
       </c>
       <c r="C118" t="s">
         <v>243</v>
       </c>
       <c r="D118" t="s">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E118" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>5</v>
       </c>
       <c r="B119">
-        <v>516</v>
+        <v>649</v>
       </c>
       <c r="C119" t="s">
         <v>245</v>
@@ -3261,199 +3261,199 @@
         <v>246</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>5</v>
       </c>
       <c r="B120">
-        <v>517</v>
+        <v>650</v>
       </c>
       <c r="C120" t="s">
         <v>247</v>
       </c>
       <c r="D120" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>5</v>
       </c>
       <c r="B121">
-        <v>518</v>
+        <v>651</v>
       </c>
       <c r="C121" t="s">
         <v>249</v>
       </c>
       <c r="D121" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>5</v>
       </c>
       <c r="B122">
-        <v>519</v>
+        <v>652</v>
       </c>
       <c r="C122" t="s">
         <v>251</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>5</v>
       </c>
       <c r="B123">
-        <v>520</v>
+        <v>653</v>
       </c>
       <c r="C123" t="s">
         <v>253</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E123" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>5</v>
       </c>
       <c r="B124">
-        <v>521</v>
+        <v>654</v>
       </c>
       <c r="C124" t="s">
         <v>255</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>5</v>
       </c>
       <c r="B125">
-        <v>522</v>
+        <v>655</v>
       </c>
       <c r="C125" t="s">
         <v>257</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E125" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>5</v>
       </c>
       <c r="B126">
-        <v>523</v>
+        <v>656</v>
       </c>
       <c r="C126" t="s">
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E126" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>5</v>
       </c>
       <c r="B127">
-        <v>524</v>
+        <v>657</v>
       </c>
       <c r="C127" t="s">
         <v>261</v>
       </c>
       <c r="D127" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>5</v>
       </c>
       <c r="B128">
-        <v>525</v>
+        <v>658</v>
       </c>
       <c r="C128" t="s">
         <v>263</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E128" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>5</v>
       </c>
       <c r="B129">
-        <v>526</v>
+        <v>659</v>
       </c>
       <c r="C129" t="s">
         <v>265</v>
       </c>
       <c r="D129" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>5</v>
       </c>
       <c r="B130">
-        <v>527</v>
+        <v>660</v>
       </c>
       <c r="C130" t="s">
         <v>267</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>5</v>
       </c>
       <c r="B131">
-        <v>528</v>
+        <v>661</v>
       </c>
       <c r="C131" t="s">
         <v>269</v>
@@ -3465,69 +3465,69 @@
         <v>270</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>5</v>
       </c>
       <c r="B132">
-        <v>529</v>
+        <v>662</v>
       </c>
       <c r="C132" t="s">
         <v>271</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>5</v>
       </c>
       <c r="B133">
-        <v>530</v>
+        <v>663</v>
       </c>
       <c r="C133" t="s">
         <v>273</v>
       </c>
       <c r="D133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>5</v>
       </c>
       <c r="B134">
-        <v>531</v>
+        <v>664</v>
       </c>
       <c r="C134" t="s">
         <v>275</v>
       </c>
       <c r="D134" t="s">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="E134" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>5</v>
       </c>
       <c r="B135">
-        <v>532</v>
+        <v>665</v>
       </c>
       <c r="C135" t="s">
         <v>277</v>
       </c>
       <c r="D135" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E135" t="s">
         <v>278</v>
